--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_005.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_005.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="182">
   <si>
     <t>Sezione</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Età(Anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
   </si>
   <si>
     <t>Provincia AIRE</t>
@@ -610,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.84375" customWidth="true" bestFit="true"/>
@@ -1918,7 +1924,7 @@
         <v>68</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>114</v>
@@ -2533,19 +2539,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2556,19 +2562,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2579,19 +2585,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2602,19 +2608,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2625,19 +2631,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2648,19 +2654,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2671,19 +2677,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2694,19 +2700,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2717,19 +2723,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2740,19 +2746,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2763,19 +2769,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2786,19 +2792,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2809,19 +2815,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2832,19 +2838,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2855,19 +2861,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2878,19 +2884,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2901,19 +2907,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2924,19 +2930,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2947,19 +2953,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2970,19 +2976,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2993,19 +2999,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3016,19 +3022,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3039,19 +3045,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3062,19 +3068,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3085,19 +3091,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3108,19 +3114,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3131,19 +3137,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3154,19 +3160,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3177,19 +3183,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3200,19 +3206,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3223,19 +3229,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3246,19 +3252,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3269,19 +3275,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3295,16 +3301,16 @@
         <v>127</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="E117" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3318,16 +3324,16 @@
         <v>127</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3338,19 +3344,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3361,19 +3367,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3384,19 +3390,19 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>10</v>
@@ -3407,19 +3413,19 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3430,19 +3436,19 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3453,19 +3459,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3476,19 +3482,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3499,19 +3505,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3522,19 +3528,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3545,19 +3551,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3568,19 +3574,19 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>10</v>
@@ -3591,19 +3597,19 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C130" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D130" s="2" t="s">
+      <c r="E130" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>10</v>
@@ -3614,19 +3620,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3637,19 +3643,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3660,19 +3666,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -3683,19 +3689,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>10</v>
@@ -3706,19 +3712,19 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>10</v>
@@ -3729,19 +3735,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3752,19 +3758,19 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
@@ -3775,19 +3781,19 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -3798,19 +3804,19 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>10</v>
@@ -3821,19 +3827,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -3847,16 +3853,16 @@
         <v>153</v>
       </c>
       <c r="B141" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="E141" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
@@ -3870,16 +3876,16 @@
         <v>153</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -3890,19 +3896,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
@@ -3913,19 +3919,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
@@ -3936,19 +3942,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>10</v>
@@ -3959,19 +3965,19 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>10</v>
@@ -3982,19 +3988,19 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>10</v>
@@ -4005,19 +4011,19 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
@@ -4028,19 +4034,19 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>10</v>
@@ -4051,19 +4057,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
@@ -4074,19 +4080,19 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>10</v>
@@ -4097,19 +4103,19 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
@@ -4120,19 +4126,19 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
@@ -4143,19 +4149,19 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>10</v>
@@ -4166,19 +4172,19 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>10</v>
@@ -4189,19 +4195,19 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="E156" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>10</v>
@@ -4212,19 +4218,19 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
@@ -4235,19 +4241,19 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
@@ -4258,24 +4264,70 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="C159" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G159" s="2" t="s">
+      <c r="B160" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" s="2" t="s">
         <v>21</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_005.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_005.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="186">
   <si>
     <t>Sezione</t>
   </si>
@@ -101,10 +101,22 @@
     <t>Dati generali</t>
   </si>
   <si>
+    <t>Formato Data Evento Matrimonio</t>
+  </si>
+  <si>
+    <t>evento.datiEventoMatrimonio</t>
+  </si>
+  <si>
+    <t>idFormatoDataEvento</t>
+  </si>
+  <si>
+    <t>Formato Data Evento Matrimonio - Descrizione</t>
+  </si>
+  <si>
+    <t>formatoDataEvento</t>
+  </si>
+  <si>
     <t>Data Evento Matrimonio</t>
-  </si>
-  <si>
-    <t>evento.datiEventoMatrimonio</t>
   </si>
   <si>
     <t>dataEvento</t>
@@ -616,11 +628,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.84375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="49.1796875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -866,7 +878,7 @@
         <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>30</v>
@@ -889,13 +901,13 @@
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>10</v>
@@ -909,16 +921,16 @@
         <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -932,13 +944,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>38</v>
@@ -961,7 +973,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>40</v>
@@ -984,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>42</v>
@@ -1007,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>44</v>
@@ -1030,7 +1042,7 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>46</v>
@@ -1050,13 +1062,13 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -1070,16 +1082,16 @@
         <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1090,19 +1102,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -1113,19 +1125,19 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -1136,19 +1148,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -1159,16 +1171,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -1182,16 +1194,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1205,7 +1217,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
@@ -1214,7 +1226,7 @@
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1228,7 +1240,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
@@ -1237,7 +1249,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1251,7 +1263,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
@@ -1260,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>69</v>
@@ -1274,16 +1286,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
@@ -1297,16 +1309,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>73</v>
@@ -1320,16 +1332,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
@@ -1343,16 +1355,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>77</v>
@@ -1366,7 +1378,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
@@ -1375,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1389,7 +1401,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1398,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1412,19 +1424,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1435,19 +1447,19 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
@@ -1458,16 +1470,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>86</v>
@@ -1481,16 +1493,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>88</v>
@@ -1504,16 +1516,16 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>90</v>
@@ -1527,7 +1539,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>91</v>
@@ -1536,7 +1548,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>92</v>
@@ -1550,7 +1562,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>93</v>
@@ -1559,7 +1571,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>94</v>
@@ -1573,7 +1585,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>95</v>
@@ -1582,7 +1594,7 @@
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>96</v>
@@ -1596,7 +1608,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>97</v>
@@ -1605,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>98</v>
@@ -1619,7 +1631,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>99</v>
@@ -1628,7 +1640,7 @@
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>100</v>
@@ -1642,7 +1654,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>101</v>
@@ -1651,7 +1663,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>102</v>
@@ -1665,7 +1677,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>103</v>
@@ -1674,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>104</v>
@@ -1688,16 +1700,16 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>106</v>
@@ -1711,16 +1723,16 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>108</v>
@@ -1734,7 +1746,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>109</v>
@@ -1743,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>110</v>
@@ -1757,16 +1769,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>112</v>
@@ -1780,19 +1792,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1803,19 +1815,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1826,16 +1838,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>61</v>
@@ -1849,7 +1861,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>62</v>
@@ -1858,7 +1870,7 @@
         <v>13</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>63</v>
@@ -1872,7 +1884,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>64</v>
@@ -1881,7 +1893,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>65</v>
@@ -1895,16 +1907,16 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>67</v>
@@ -1918,7 +1930,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>68</v>
@@ -1927,7 +1939,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>69</v>
@@ -1941,16 +1953,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>71</v>
@@ -1964,16 +1976,16 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>73</v>
@@ -1987,16 +1999,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>75</v>
@@ -2010,16 +2022,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>77</v>
@@ -2033,7 +2045,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>78</v>
@@ -2042,7 +2054,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>79</v>
@@ -2056,7 +2068,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>80</v>
@@ -2065,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>81</v>
@@ -2079,19 +2091,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2102,19 +2114,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2125,16 +2137,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>86</v>
@@ -2148,16 +2160,16 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>88</v>
@@ -2171,16 +2183,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>90</v>
@@ -2194,7 +2206,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>91</v>
@@ -2203,7 +2215,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>92</v>
@@ -2217,7 +2229,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>93</v>
@@ -2226,7 +2238,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>94</v>
@@ -2240,7 +2252,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>95</v>
@@ -2249,7 +2261,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>96</v>
@@ -2263,7 +2275,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>97</v>
@@ -2272,7 +2284,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>98</v>
@@ -2286,7 +2298,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>99</v>
@@ -2295,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>100</v>
@@ -2309,7 +2321,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>101</v>
@@ -2318,7 +2330,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>102</v>
@@ -2332,7 +2344,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>103</v>
@@ -2341,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>104</v>
@@ -2355,16 +2367,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>106</v>
@@ -2378,16 +2390,16 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>108</v>
@@ -2401,7 +2413,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>109</v>
@@ -2410,7 +2422,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>110</v>
@@ -2424,19 +2436,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2447,19 +2459,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2470,7 +2482,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>119</v>
@@ -2479,7 +2491,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>120</v>
@@ -2493,7 +2505,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>121</v>
@@ -2502,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>122</v>
@@ -2516,7 +2528,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>123</v>
@@ -2525,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>124</v>
@@ -2539,7 +2551,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>125</v>
@@ -2548,7 +2560,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>126</v>
@@ -2562,19 +2574,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2585,19 +2597,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2608,16 +2620,16 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>61</v>
@@ -2631,7 +2643,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>62</v>
@@ -2640,7 +2652,7 @@
         <v>13</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>63</v>
@@ -2654,7 +2666,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>64</v>
@@ -2663,7 +2675,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>65</v>
@@ -2677,16 +2689,16 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>67</v>
@@ -2700,7 +2712,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>68</v>
@@ -2709,7 +2721,7 @@
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>69</v>
@@ -2723,16 +2735,16 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>71</v>
@@ -2746,16 +2758,16 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>73</v>
@@ -2769,16 +2781,16 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>75</v>
@@ -2792,16 +2804,16 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>77</v>
@@ -2815,7 +2827,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>78</v>
@@ -2824,7 +2836,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>79</v>
@@ -2838,7 +2850,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>80</v>
@@ -2847,7 +2859,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>81</v>
@@ -2861,19 +2873,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2884,19 +2896,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2907,16 +2919,16 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>86</v>
@@ -2930,16 +2942,16 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>88</v>
@@ -2953,16 +2965,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>90</v>
@@ -2976,7 +2988,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>91</v>
@@ -2985,7 +2997,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>92</v>
@@ -2999,7 +3011,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>93</v>
@@ -3008,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>94</v>
@@ -3022,7 +3034,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>95</v>
@@ -3031,7 +3043,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>96</v>
@@ -3045,7 +3057,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>97</v>
@@ -3054,7 +3066,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>98</v>
@@ -3068,7 +3080,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>99</v>
@@ -3077,7 +3089,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>100</v>
@@ -3091,7 +3103,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>101</v>
@@ -3100,7 +3112,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>102</v>
@@ -3114,7 +3126,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>103</v>
@@ -3123,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>104</v>
@@ -3137,16 +3149,16 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>106</v>
@@ -3160,16 +3172,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>108</v>
@@ -3183,7 +3195,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>109</v>
@@ -3192,7 +3204,7 @@
         <v>13</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>110</v>
@@ -3206,19 +3218,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3229,19 +3241,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3252,7 +3264,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>119</v>
@@ -3261,7 +3273,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>120</v>
@@ -3275,7 +3287,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>121</v>
@@ -3284,7 +3296,7 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>122</v>
@@ -3298,7 +3310,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>123</v>
@@ -3307,7 +3319,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>124</v>
@@ -3321,7 +3333,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>125</v>
@@ -3330,7 +3342,7 @@
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>126</v>
@@ -3344,19 +3356,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3367,19 +3379,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3390,16 +3402,16 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>136</v>
@@ -3413,7 +3425,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>137</v>
@@ -3422,7 +3434,7 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>138</v>
@@ -3436,7 +3448,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>139</v>
@@ -3445,7 +3457,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>140</v>
@@ -3459,7 +3471,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>141</v>
@@ -3468,10 +3480,10 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3482,19 +3494,19 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3505,19 +3517,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3528,19 +3540,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>10</v>
@@ -3551,19 +3563,19 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>10</v>
@@ -3574,7 +3586,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>149</v>
@@ -3583,7 +3595,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>150</v>
@@ -3597,7 +3609,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>151</v>
@@ -3606,7 +3618,7 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>152</v>
@@ -3620,19 +3632,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="C131" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3643,19 +3655,19 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>10</v>
@@ -3666,16 +3678,16 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>136</v>
@@ -3689,7 +3701,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>137</v>
@@ -3698,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>138</v>
@@ -3712,7 +3724,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>139</v>
@@ -3721,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>140</v>
@@ -3735,7 +3747,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>141</v>
@@ -3744,10 +3756,10 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>10</v>
@@ -3758,19 +3770,19 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
@@ -3781,19 +3793,19 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -3804,19 +3816,19 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>10</v>
@@ -3827,19 +3839,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -3850,7 +3862,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>149</v>
@@ -3859,7 +3871,7 @@
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>150</v>
@@ -3873,7 +3885,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>151</v>
@@ -3882,7 +3894,7 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>152</v>
@@ -3896,19 +3908,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
@@ -3919,19 +3931,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="C144" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
@@ -3942,16 +3954,16 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>162</v>
@@ -3965,7 +3977,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>163</v>
@@ -3974,7 +3986,7 @@
         <v>13</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>164</v>
@@ -3988,7 +4000,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>165</v>
@@ -3997,7 +4009,7 @@
         <v>13</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>166</v>
@@ -4011,16 +4023,16 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>168</v>
@@ -4034,16 +4046,16 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>170</v>
@@ -4057,7 +4069,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>171</v>
@@ -4066,7 +4078,7 @@
         <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>172</v>
@@ -4080,7 +4092,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>173</v>
@@ -4089,7 +4101,7 @@
         <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>174</v>
@@ -4103,19 +4115,19 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>45</v>
+        <v>175</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>46</v>
+        <v>176</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
@@ -4126,19 +4138,19 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
@@ -4149,19 +4161,19 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>10</v>
@@ -4172,16 +4184,16 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>166</v>
@@ -4195,16 +4207,16 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>168</v>
@@ -4218,16 +4230,16 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>170</v>
@@ -4241,16 +4253,16 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>172</v>
@@ -4264,7 +4276,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>173</v>
@@ -4273,7 +4285,7 @@
         <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>174</v>
@@ -4287,19 +4299,19 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>10</v>
@@ -4310,24 +4322,70 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="2" t="s">
         <v>21</v>
       </c>
     </row>
